--- a/dados.xlsx
+++ b/dados.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mutuus09\Desktop\Doc. Salvar Drive\NOMYNAL\REPORT FINANCEIRO\Apresentação\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88861C4E-9754-4A49-9315-47CC599FAFD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2125DC78-66BC-43F9-88C4-D7096DF00A5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{F0C8FD1A-3145-4E83-BD6B-DC10C4D6167D}"/>
   </bookViews>
@@ -21,8 +21,8 @@
     <sheet name="INADIMPLENTES" sheetId="8" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="DadosExternos_5" localSheetId="1" hidden="1">'Receitas'!$A$1:$C$55</definedName>
-    <definedName name="DadosExternos_6" localSheetId="2" hidden="1">Saldos!$A$1:$C$91</definedName>
+    <definedName name="DadosExternos_5" localSheetId="1" hidden="1">'Receitas'!$A$1:$C$58</definedName>
+    <definedName name="DadosExternos_6" localSheetId="2" hidden="1">Saldos!$A$1:$C$96</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2424" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2482" uniqueCount="164">
   <si>
     <t>Período</t>
   </si>
@@ -469,85 +469,19 @@
     <t>MARCOS RODRIGO CORNÉLIO DE BRITO</t>
   </si>
   <si>
-    <t>SIMÃO FREITAS</t>
-  </si>
-  <si>
-    <t>FERNANDO MASSAFERA CAMPEÃO</t>
-  </si>
-  <si>
-    <t>THIAGO RIBEIRO</t>
-  </si>
-  <si>
     <t>WR ENGENHARIA ELETRICA E REFRIGERAÇÃO</t>
   </si>
   <si>
     <t>NEW ENERGY PROJETOS E CONSULTORIA LTDA</t>
   </si>
   <si>
-    <t>01/09/2025</t>
-  </si>
-  <si>
-    <t>01/10/2025</t>
-  </si>
-  <si>
-    <t>24/03/2025</t>
-  </si>
-  <si>
-    <t>01/11/2025</t>
-  </si>
-  <si>
-    <t>01/01/2026</t>
-  </si>
-  <si>
-    <t>27/05/2026</t>
-  </si>
-  <si>
-    <t>12/06/2026</t>
-  </si>
-  <si>
-    <t>01/06/2026</t>
-  </si>
-  <si>
-    <t>05/07/2026</t>
-  </si>
-  <si>
-    <t>16/04/2026</t>
-  </si>
-  <si>
-    <t>12/07/2026</t>
-  </si>
-  <si>
-    <t>27/07/2026</t>
-  </si>
-  <si>
     <t>05/08/2026</t>
-  </si>
-  <si>
-    <t>04/08/2026</t>
   </si>
   <si>
     <t>08/08/2026</t>
   </si>
   <si>
     <t>07/08/2026</t>
-  </si>
-  <si>
-    <t>12/08/2026</t>
-  </si>
-  <si>
-    <t>15/08/2026</t>
-  </si>
-  <si>
-    <t>14/08/2026</t>
-  </si>
-  <si>
-    <t>17/08/2026</t>
-  </si>
-  <si>
-    <t>19/08/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AAFELIX COMERCIO, MONTAGENS E INSTALACOES </t>
   </si>
   <si>
     <t>Especialista Reyrolle</t>
@@ -559,10 +493,70 @@
     <t xml:space="preserve">Formação MESH </t>
   </si>
   <si>
-    <t>PRESENCIAL ESTUDOS E ENSAIOS #03.2026</t>
+    <t xml:space="preserve">Presencial Estudos e Ensaios </t>
   </si>
   <si>
-    <t xml:space="preserve">PRESENCIAL ESTUDOS E ENSAIOS #04.26 </t>
+    <t>AAFELIX COMERCIO, MONTAGENS E INSTALACOES E</t>
+  </si>
+  <si>
+    <t>NICOLAS ANTUNES NEVES</t>
+  </si>
+  <si>
+    <t>20/09/2025</t>
+  </si>
+  <si>
+    <t>20/10/2025</t>
+  </si>
+  <si>
+    <t>05/12/2025</t>
+  </si>
+  <si>
+    <t>31/12/2025</t>
+  </si>
+  <si>
+    <t>30/01/2026</t>
+  </si>
+  <si>
+    <t>29/05/2026</t>
+  </si>
+  <si>
+    <t>13/06/2026</t>
+  </si>
+  <si>
+    <t>20/06/2026</t>
+  </si>
+  <si>
+    <t>07/07/2026</t>
+  </si>
+  <si>
+    <t>10/07/2026</t>
+  </si>
+  <si>
+    <t>13/07/2026</t>
+  </si>
+  <si>
+    <t>29/07/2026</t>
+  </si>
+  <si>
+    <t>13/08/2026</t>
+  </si>
+  <si>
+    <t>18/08/2026</t>
+  </si>
+  <si>
+    <t>20/08/2026</t>
+  </si>
+  <si>
+    <t>05/09/2026</t>
+  </si>
+  <si>
+    <t>11/09/2026</t>
+  </si>
+  <si>
+    <t>20/09/2026</t>
+  </si>
+  <si>
+    <t>30/09/2026</t>
   </si>
 </sst>
 </file>
@@ -856,7 +850,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
@@ -909,13 +903,12 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="17" fontId="4" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="17" fontId="4" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1127,8 +1120,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{EB327D28-BF5F-44AF-9542-154E1B1AB8FF}" name="Cursos" displayName="Cursos" ref="A1:C140" totalsRowShown="0">
-  <autoFilter ref="A1:C140" xr:uid="{EB327D28-BF5F-44AF-9542-154E1B1AB8FF}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{EB327D28-BF5F-44AF-9542-154E1B1AB8FF}" name="Cursos" displayName="Cursos" ref="A1:C144" totalsRowShown="0">
+  <autoFilter ref="A1:C144" xr:uid="{EB327D28-BF5F-44AF-9542-154E1B1AB8FF}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{8ED6A9AC-5546-48C4-A9FF-C7F22FA66E77}" name="Período" dataDxfId="11"/>
     <tableColumn id="51" xr3:uid="{E07EBCDC-B1A7-45EA-BBEB-E92DAB44E662}" name="Curso" dataDxfId="10"/>
@@ -1139,11 +1132,11 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{FDED0B91-D832-4031-B569-DA6CDBA6BDA7}" name="Receitas" displayName="Receitas" ref="A1:C55" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:C55" xr:uid="{FDED0B91-D832-4031-B569-DA6CDBA6BDA7}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{FDED0B91-D832-4031-B569-DA6CDBA6BDA7}" name="Receitas" displayName="Receitas" ref="A1:C58" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:C58" xr:uid="{FDED0B91-D832-4031-B569-DA6CDBA6BDA7}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{53746AEF-FC3F-47E5-BE01-B0D268A71582}" uniqueName="1" name="Período" queryTableFieldId="1" dataDxfId="9"/>
-    <tableColumn id="58" xr3:uid="{21EA503D-7D30-45A5-839B-1E68218EB0D2}" uniqueName="58" name="Fonte de Recebimento" queryTableFieldId="58" dataDxfId="8"/>
+    <tableColumn id="1" xr3:uid="{53746AEF-FC3F-47E5-BE01-B0D268A71582}" uniqueName="1" name="Período" queryTableFieldId="1" dataDxfId="7"/>
+    <tableColumn id="58" xr3:uid="{21EA503D-7D30-45A5-839B-1E68218EB0D2}" uniqueName="58" name="Fonte de Recebimento" queryTableFieldId="58" dataDxfId="6"/>
     <tableColumn id="59" xr3:uid="{27235FC9-4C75-4E95-B45C-47EEFEAA8B84}" uniqueName="59" name="Recebimentos Consolidados" queryTableFieldId="59" dataCellStyle="Vírgula"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1151,11 +1144,11 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{F06FB0DD-EA40-4E16-9421-9973550E4B68}" name="Saldos" displayName="Saldos" ref="A1:C91" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:C91" xr:uid="{F06FB0DD-EA40-4E16-9421-9973550E4B68}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{F06FB0DD-EA40-4E16-9421-9973550E4B68}" name="Saldos" displayName="Saldos" ref="A1:C96" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:C96" xr:uid="{F06FB0DD-EA40-4E16-9421-9973550E4B68}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{E75689D2-A981-46E0-9922-1539179AB3A6}" uniqueName="1" name="Período" queryTableFieldId="1" dataDxfId="7"/>
-    <tableColumn id="56" xr3:uid="{7268ECC7-D64E-4533-A47C-D94E0EB4057A}" uniqueName="56" name="Saldo por Contas" queryTableFieldId="56" dataDxfId="6"/>
+    <tableColumn id="1" xr3:uid="{E75689D2-A981-46E0-9922-1539179AB3A6}" uniqueName="1" name="Período" queryTableFieldId="1" dataDxfId="9"/>
+    <tableColumn id="56" xr3:uid="{7268ECC7-D64E-4533-A47C-D94E0EB4057A}" uniqueName="56" name="Saldo por Contas" queryTableFieldId="56" dataDxfId="8"/>
     <tableColumn id="57" xr3:uid="{CB647634-C9D4-4FA0-8BF7-80EB0BBF8BED}" uniqueName="57" name="Saldo Total das Contas" queryTableFieldId="57" dataCellStyle="Vírgula"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1163,8 +1156,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{0CB9FD63-5164-48E2-BF8E-4926B4D280BD}" name="Tabela6" displayName="Tabela6" ref="A1:D975" totalsRowShown="0">
-  <autoFilter ref="A1:D975" xr:uid="{0CB9FD63-5164-48E2-BF8E-4926B4D280BD}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{0CB9FD63-5164-48E2-BF8E-4926B4D280BD}" name="Tabela6" displayName="Tabela6" ref="A1:D998" totalsRowShown="0">
+  <autoFilter ref="A1:D998" xr:uid="{0CB9FD63-5164-48E2-BF8E-4926B4D280BD}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{A39CAD23-7B43-45FD-9823-777EBDF11FD6}" name="Mês/Ano"/>
     <tableColumn id="2" xr3:uid="{C5551780-11CE-4848-872C-7C9D3092E5B1}" name="Centro de custo"/>
@@ -1504,7 +1497,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21F57F01-F8AB-48CC-9DC9-B631A8439A38}">
-  <dimension ref="A1:E140"/>
+  <dimension ref="A1:E144"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -3005,8 +2998,8 @@
       <c r="A136" s="1">
         <v>46235</v>
       </c>
-      <c r="B136" s="46" t="s">
-        <v>161</v>
+      <c r="B136" t="s">
+        <v>139</v>
       </c>
       <c r="C136" s="2">
         <v>497</v>
@@ -3016,44 +3009,88 @@
       <c r="A137" s="1">
         <v>46235</v>
       </c>
-      <c r="B137" s="46" t="s">
-        <v>162</v>
+      <c r="B137" t="s">
+        <v>140</v>
       </c>
       <c r="C137" s="2">
-        <v>2930.18</v>
+        <v>6029.3</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" s="1">
         <v>46235</v>
       </c>
-      <c r="B138" s="46" t="s">
-        <v>163</v>
+      <c r="B138" t="s">
+        <v>141</v>
       </c>
       <c r="C138" s="2">
-        <v>37951.19</v>
+        <v>43174.04</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" s="1">
         <v>46235</v>
       </c>
-      <c r="B139" s="46" t="s">
-        <v>164</v>
+      <c r="B139" t="s">
+        <v>142</v>
       </c>
       <c r="C139" s="2">
-        <v>1050.75</v>
+        <v>11635.5</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" s="1">
-        <v>46235</v>
-      </c>
-      <c r="B140" s="46" t="s">
-        <v>165</v>
+        <v>46266</v>
+      </c>
+      <c r="B140" t="s">
+        <v>3</v>
       </c>
       <c r="C140" s="2">
-        <v>6013.77</v>
+        <v>5210.67</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A141" s="1">
+        <v>46266</v>
+      </c>
+      <c r="B141" t="s">
+        <v>139</v>
+      </c>
+      <c r="C141" s="2">
+        <v>550.25</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A142" s="1">
+        <v>46266</v>
+      </c>
+      <c r="B142" t="s">
+        <v>140</v>
+      </c>
+      <c r="C142" s="2">
+        <v>1365.37</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A143" s="1">
+        <v>46266</v>
+      </c>
+      <c r="B143" t="s">
+        <v>141</v>
+      </c>
+      <c r="C143" s="2">
+        <v>19456.439999999999</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A144" s="1">
+        <v>46266</v>
+      </c>
+      <c r="B144" t="s">
+        <v>142</v>
+      </c>
+      <c r="C144" s="2">
+        <v>17934.12</v>
       </c>
     </row>
   </sheetData>
@@ -3066,7 +3103,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{168247FE-0B74-422F-9ED0-046BEB0B4F2B}">
-  <dimension ref="A1:C55"/>
+  <dimension ref="A1:C58"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -3676,7 +3713,40 @@
         <v>16</v>
       </c>
       <c r="C55" s="2">
-        <v>23167.74</v>
+        <v>25161.86</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="1">
+        <v>46266</v>
+      </c>
+      <c r="B56" t="s">
+        <v>14</v>
+      </c>
+      <c r="C56" s="2">
+        <v>17511.150000000001</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="1">
+        <v>46266</v>
+      </c>
+      <c r="B57" t="s">
+        <v>15</v>
+      </c>
+      <c r="C57" s="2">
+        <v>14571.63</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="1">
+        <v>46266</v>
+      </c>
+      <c r="B58" t="s">
+        <v>16</v>
+      </c>
+      <c r="C58" s="2">
+        <v>18280.62</v>
       </c>
     </row>
   </sheetData>
@@ -3689,7 +3759,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE148E52-2023-4B1D-BCCE-9B6146F0E619}">
-  <dimension ref="A1:C91"/>
+  <dimension ref="A1:C96"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -4647,7 +4717,7 @@
       <c r="A87" s="1">
         <v>46235</v>
       </c>
-      <c r="B87" s="46" t="s">
+      <c r="B87" t="s">
         <v>19</v>
       </c>
       <c r="C87" s="2">
@@ -4669,7 +4739,7 @@
       <c r="A89" s="1">
         <v>46235</v>
       </c>
-      <c r="B89" s="46" t="s">
+      <c r="B89" t="s">
         <v>21</v>
       </c>
       <c r="C89" s="2">
@@ -4680,7 +4750,7 @@
       <c r="A90" s="1">
         <v>46235</v>
       </c>
-      <c r="B90" s="46" t="s">
+      <c r="B90" t="s">
         <v>22</v>
       </c>
       <c r="C90" s="2">
@@ -4691,11 +4761,66 @@
       <c r="A91" s="1">
         <v>46235</v>
       </c>
-      <c r="B91" s="46" t="s">
+      <c r="B91" t="s">
         <v>23</v>
       </c>
       <c r="C91" s="2">
         <v>27714.82</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" s="1">
+        <v>46266</v>
+      </c>
+      <c r="B92" t="s">
+        <v>19</v>
+      </c>
+      <c r="C92" s="2">
+        <v>19376.060000000001</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" s="1">
+        <v>46266</v>
+      </c>
+      <c r="B93" t="s">
+        <v>20</v>
+      </c>
+      <c r="C93" s="2">
+        <v>153775.44</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" s="1">
+        <v>46266</v>
+      </c>
+      <c r="B94" t="s">
+        <v>21</v>
+      </c>
+      <c r="C94" s="2">
+        <v>747.06</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" s="1">
+        <v>46266</v>
+      </c>
+      <c r="B95" t="s">
+        <v>22</v>
+      </c>
+      <c r="C95" s="2">
+        <v>163845.73000000001</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" s="1">
+        <v>46266</v>
+      </c>
+      <c r="B96" t="s">
+        <v>23</v>
+      </c>
+      <c r="C96" s="2">
+        <v>27954.58</v>
       </c>
     </row>
   </sheetData>
@@ -4708,7 +4833,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{330E1BF0-0B3C-450F-98E3-02BBA56597B7}">
-  <dimension ref="A1:D975"/>
+  <dimension ref="A1:D998"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.85546875" customWidth="1"/>
@@ -18365,6 +18490,328 @@
       </c>
       <c r="D975" s="2">
         <v>1.99</v>
+      </c>
+    </row>
+    <row r="976" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A976" s="43">
+        <v>46266</v>
+      </c>
+      <c r="B976" t="s">
+        <v>118</v>
+      </c>
+      <c r="C976" t="s">
+        <v>42</v>
+      </c>
+      <c r="D976" s="2">
+        <v>59247.96</v>
+      </c>
+    </row>
+    <row r="977" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A977" s="43">
+        <v>46266</v>
+      </c>
+      <c r="B977" t="s">
+        <v>118</v>
+      </c>
+      <c r="C977" t="s">
+        <v>66</v>
+      </c>
+      <c r="D977" s="2">
+        <v>5.07</v>
+      </c>
+    </row>
+    <row r="978" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A978" s="43">
+        <v>46266</v>
+      </c>
+      <c r="B978" t="s">
+        <v>115</v>
+      </c>
+      <c r="C978" t="s">
+        <v>77</v>
+      </c>
+      <c r="D978" s="2">
+        <v>24220</v>
+      </c>
+    </row>
+    <row r="979" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A979" s="43">
+        <v>46266</v>
+      </c>
+      <c r="B979" t="s">
+        <v>115</v>
+      </c>
+      <c r="C979" t="s">
+        <v>40</v>
+      </c>
+      <c r="D979" s="2">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="980" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A980" s="43">
+        <v>46266</v>
+      </c>
+      <c r="B980" t="s">
+        <v>115</v>
+      </c>
+      <c r="C980" t="s">
+        <v>58</v>
+      </c>
+      <c r="D980" s="2">
+        <v>1442.69</v>
+      </c>
+    </row>
+    <row r="981" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A981" s="43">
+        <v>46266</v>
+      </c>
+      <c r="B981" t="s">
+        <v>115</v>
+      </c>
+      <c r="C981" t="s">
+        <v>47</v>
+      </c>
+      <c r="D981" s="2">
+        <v>637.70000000000005</v>
+      </c>
+    </row>
+    <row r="982" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A982" s="43">
+        <v>46266</v>
+      </c>
+      <c r="B982" t="s">
+        <v>115</v>
+      </c>
+      <c r="C982" t="s">
+        <v>66</v>
+      </c>
+      <c r="D982" s="2">
+        <v>124.66</v>
+      </c>
+    </row>
+    <row r="983" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A983" s="43">
+        <v>46266</v>
+      </c>
+      <c r="B983" t="s">
+        <v>115</v>
+      </c>
+      <c r="C983" t="s">
+        <v>73</v>
+      </c>
+      <c r="D983" s="2">
+        <v>42.15</v>
+      </c>
+    </row>
+    <row r="984" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A984" s="43">
+        <v>46266</v>
+      </c>
+      <c r="B984" t="s">
+        <v>115</v>
+      </c>
+      <c r="C984" t="s">
+        <v>55</v>
+      </c>
+      <c r="D984" s="2">
+        <v>33.47</v>
+      </c>
+    </row>
+    <row r="985" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A985" s="43">
+        <v>46266</v>
+      </c>
+      <c r="B985" t="s">
+        <v>117</v>
+      </c>
+      <c r="C985" t="s">
+        <v>39</v>
+      </c>
+      <c r="D985" s="2">
+        <v>9045.48</v>
+      </c>
+    </row>
+    <row r="986" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A986" s="43">
+        <v>46266</v>
+      </c>
+      <c r="B986" t="s">
+        <v>119</v>
+      </c>
+      <c r="C986" t="s">
+        <v>42</v>
+      </c>
+      <c r="D986" s="2">
+        <v>5500</v>
+      </c>
+    </row>
+    <row r="987" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A987" s="43">
+        <v>46266</v>
+      </c>
+      <c r="B987" t="s">
+        <v>119</v>
+      </c>
+      <c r="C987" t="s">
+        <v>66</v>
+      </c>
+      <c r="D987" s="2">
+        <v>789.99</v>
+      </c>
+    </row>
+    <row r="988" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A988" s="43">
+        <v>46266</v>
+      </c>
+      <c r="B988" t="s">
+        <v>120</v>
+      </c>
+      <c r="C988" t="s">
+        <v>110</v>
+      </c>
+      <c r="D988" s="2">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="989" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A989" s="43">
+        <v>46266</v>
+      </c>
+      <c r="B989" t="s">
+        <v>116</v>
+      </c>
+      <c r="C989" t="s">
+        <v>50</v>
+      </c>
+      <c r="D989" s="2">
+        <v>1350</v>
+      </c>
+    </row>
+    <row r="990" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A990" s="43">
+        <v>46266</v>
+      </c>
+      <c r="B990" t="s">
+        <v>116</v>
+      </c>
+      <c r="C990" t="s">
+        <v>52</v>
+      </c>
+      <c r="D990" s="2">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="991" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A991" s="43">
+        <v>46266</v>
+      </c>
+      <c r="B991" t="s">
+        <v>116</v>
+      </c>
+      <c r="C991" t="s">
+        <v>49</v>
+      </c>
+      <c r="D991" s="2">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="992" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A992" s="43">
+        <v>46266</v>
+      </c>
+      <c r="B992" t="s">
+        <v>116</v>
+      </c>
+      <c r="C992" t="s">
+        <v>51</v>
+      </c>
+      <c r="D992" s="2">
+        <v>327.51</v>
+      </c>
+    </row>
+    <row r="993" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A993" s="43">
+        <v>46266</v>
+      </c>
+      <c r="B993" t="s">
+        <v>116</v>
+      </c>
+      <c r="C993" t="s">
+        <v>65</v>
+      </c>
+      <c r="D993" s="2">
+        <v>227.88</v>
+      </c>
+    </row>
+    <row r="994" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A994" s="43">
+        <v>46266</v>
+      </c>
+      <c r="B994" t="s">
+        <v>116</v>
+      </c>
+      <c r="C994" t="s">
+        <v>53</v>
+      </c>
+      <c r="D994" s="2">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="995" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A995" s="43">
+        <v>46266</v>
+      </c>
+      <c r="B995" t="s">
+        <v>116</v>
+      </c>
+      <c r="C995" t="s">
+        <v>57</v>
+      </c>
+      <c r="D995" s="2">
+        <v>178.31</v>
+      </c>
+    </row>
+    <row r="996" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A996" s="43">
+        <v>46266</v>
+      </c>
+      <c r="B996" t="s">
+        <v>116</v>
+      </c>
+      <c r="C996" t="s">
+        <v>54</v>
+      </c>
+      <c r="D996" s="2">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="997" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A997" s="43">
+        <v>46266</v>
+      </c>
+      <c r="B997" t="s">
+        <v>116</v>
+      </c>
+      <c r="C997" t="s">
+        <v>40</v>
+      </c>
+      <c r="D997" s="2">
+        <v>124.15</v>
+      </c>
+    </row>
+    <row r="998" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A998" s="43">
+        <v>46266</v>
+      </c>
+      <c r="B998" t="s">
+        <v>116</v>
+      </c>
+      <c r="C998" t="s">
+        <v>66</v>
+      </c>
+      <c r="D998" s="2">
+        <v>27.99</v>
       </c>
     </row>
   </sheetData>
@@ -18381,7 +18828,9 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="56.5703125" customWidth="1"/>
-    <col min="2" max="47" width="15.7109375" customWidth="1"/>
+    <col min="2" max="39" width="15.7109375" hidden="1" customWidth="1"/>
+    <col min="40" max="41" width="15.7109375" customWidth="1"/>
+    <col min="42" max="47" width="15.7109375" hidden="1" customWidth="1"/>
     <col min="48" max="49" width="16.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -18389,102 +18838,102 @@
       <c r="A1" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="45">
+      <c r="B1" s="44">
         <v>45689</v>
       </c>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45">
+      <c r="C1" s="44"/>
+      <c r="D1" s="44">
         <v>45717</v>
       </c>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45">
+      <c r="E1" s="44"/>
+      <c r="F1" s="44">
         <v>45748</v>
       </c>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45">
+      <c r="G1" s="44"/>
+      <c r="H1" s="44">
         <v>45778</v>
       </c>
-      <c r="I1" s="45"/>
-      <c r="J1" s="45">
+      <c r="I1" s="44"/>
+      <c r="J1" s="44">
         <v>45809</v>
       </c>
-      <c r="K1" s="45"/>
-      <c r="L1" s="45">
+      <c r="K1" s="44"/>
+      <c r="L1" s="44">
         <v>45839</v>
       </c>
-      <c r="M1" s="45"/>
-      <c r="N1" s="45">
+      <c r="M1" s="44"/>
+      <c r="N1" s="44">
         <v>45870</v>
       </c>
-      <c r="O1" s="45"/>
-      <c r="P1" s="45">
+      <c r="O1" s="44"/>
+      <c r="P1" s="44">
         <v>45901</v>
       </c>
-      <c r="Q1" s="45"/>
-      <c r="R1" s="45">
+      <c r="Q1" s="44"/>
+      <c r="R1" s="44">
         <v>45931</v>
       </c>
-      <c r="S1" s="45"/>
-      <c r="T1" s="45">
+      <c r="S1" s="44"/>
+      <c r="T1" s="44">
         <v>45962</v>
       </c>
-      <c r="U1" s="45"/>
-      <c r="V1" s="45">
+      <c r="U1" s="44"/>
+      <c r="V1" s="44">
         <v>45992</v>
       </c>
-      <c r="W1" s="45"/>
-      <c r="X1" s="45">
+      <c r="W1" s="44"/>
+      <c r="X1" s="44">
         <v>46023</v>
       </c>
-      <c r="Y1" s="45"/>
-      <c r="Z1" s="45">
+      <c r="Y1" s="44"/>
+      <c r="Z1" s="44">
         <v>46054</v>
       </c>
-      <c r="AA1" s="45"/>
-      <c r="AB1" s="45">
+      <c r="AA1" s="44"/>
+      <c r="AB1" s="44">
         <v>46082</v>
       </c>
-      <c r="AC1" s="45"/>
-      <c r="AD1" s="45">
+      <c r="AC1" s="44"/>
+      <c r="AD1" s="44">
         <v>46113</v>
       </c>
-      <c r="AE1" s="45"/>
-      <c r="AF1" s="45">
+      <c r="AE1" s="44"/>
+      <c r="AF1" s="44">
         <v>46143</v>
       </c>
-      <c r="AG1" s="45"/>
-      <c r="AH1" s="45">
+      <c r="AG1" s="44"/>
+      <c r="AH1" s="44">
         <v>46174</v>
       </c>
-      <c r="AI1" s="45"/>
-      <c r="AJ1" s="45">
+      <c r="AI1" s="44"/>
+      <c r="AJ1" s="44">
         <v>46204</v>
       </c>
-      <c r="AK1" s="45"/>
-      <c r="AL1" s="45">
+      <c r="AK1" s="44"/>
+      <c r="AL1" s="44">
         <v>46235</v>
       </c>
-      <c r="AM1" s="45"/>
-      <c r="AN1" s="45">
+      <c r="AM1" s="44"/>
+      <c r="AN1" s="44">
         <v>46266</v>
       </c>
-      <c r="AO1" s="45"/>
-      <c r="AP1" s="45">
+      <c r="AO1" s="44"/>
+      <c r="AP1" s="44">
         <v>46296</v>
       </c>
-      <c r="AQ1" s="45"/>
-      <c r="AR1" s="45">
+      <c r="AQ1" s="44"/>
+      <c r="AR1" s="44">
         <v>46327</v>
       </c>
-      <c r="AS1" s="45"/>
-      <c r="AT1" s="45">
+      <c r="AS1" s="44"/>
+      <c r="AT1" s="44">
         <v>46357</v>
       </c>
-      <c r="AU1" s="45"/>
-      <c r="AV1" s="44" t="s">
+      <c r="AU1" s="44"/>
+      <c r="AV1" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="AW1" s="44"/>
+      <c r="AW1" s="45"/>
     </row>
     <row r="2" spans="1:49" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="21" t="s">
@@ -18754,10 +19203,10 @@
         <v>430173.37</v>
       </c>
       <c r="AN3" s="5">
-        <v>647094.52</v>
+        <v>602807.21</v>
       </c>
       <c r="AO3" s="5">
-        <v>444032.13</v>
+        <v>422919.12</v>
       </c>
       <c r="AP3" s="5">
         <v>650579.51</v>
@@ -18903,10 +19352,10 @@
         <v>80120.289999999994</v>
       </c>
       <c r="AN4" s="6">
-        <v>30877.74</v>
+        <v>58389.440000000002</v>
       </c>
       <c r="AO4" s="6">
-        <v>0</v>
+        <v>54204.63</v>
       </c>
       <c r="AP4" s="6">
         <v>10856.35</v>
@@ -18928,11 +19377,11 @@
       </c>
       <c r="AV4" s="6">
         <f>SUM(B4+D4+F4+H4+J4+L4+N4+P4+R4+T4+V4+X4+Z4+AB4+AD4+AF4+AH4+AJ4+AL4+AN4+AP4+AR4+AT4)</f>
-        <v>1911910.94</v>
+        <v>1939422.64</v>
       </c>
       <c r="AW4" s="26">
         <f>SUM(C4+E4+G4+I4+K4+M4+O4+Q4+S4+U4+W4+Y4+AA4+AC4+AE4+AG4+AI4+AK4+AM4+AO4+AQ4+AS4+AU4)</f>
-        <v>1677091.7700000003</v>
+        <v>1731296.4000000001</v>
       </c>
     </row>
     <row r="5" spans="1:49" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -19054,10 +19503,10 @@
         <v>67259.81</v>
       </c>
       <c r="AN5" s="7">
-        <v>30877.74</v>
+        <v>57361.42</v>
       </c>
       <c r="AO5" s="7">
-        <v>0</v>
+        <v>53206.080000000002</v>
       </c>
       <c r="AP5" s="7">
         <v>10856.35</v>
@@ -19079,11 +19528,11 @@
       </c>
       <c r="AV5" s="7">
         <f t="shared" ref="AV5:AV68" si="0">SUM(B5+D5+F5+H5+J5+L5+N5+P5+R5+T5+V5+X5+Z5+AB5+AD5+AF5+AH5+AJ5+AL5+AN5+AP5+AR5+AT5)</f>
-        <v>1735116.4800000002</v>
+        <v>1761600.1600000001</v>
       </c>
       <c r="AW5" s="28">
         <f t="shared" ref="AW5:AW68" si="1">SUM(C5+E5+G5+I5+K5+M5+O5+Q5+S5+U5+W5+Y5+AA5+AC5+AE5+AG5+AI5+AK5+AM5+AO5+AQ5+AS5+AU5)</f>
-        <v>1500267.84</v>
+        <v>1553473.9200000002</v>
       </c>
     </row>
     <row r="6" spans="1:49" x14ac:dyDescent="0.25">
@@ -19356,10 +19805,10 @@
         <v>67259.81</v>
       </c>
       <c r="AN7" s="8">
-        <v>30877.74</v>
+        <v>57361.42</v>
       </c>
       <c r="AO7" s="9">
-        <v>0</v>
+        <v>53206.080000000002</v>
       </c>
       <c r="AP7" s="8">
         <v>10856.35</v>
@@ -19381,11 +19830,11 @@
       </c>
       <c r="AV7" s="8">
         <f t="shared" si="0"/>
-        <v>1730116.4800000002</v>
+        <v>1756600.1600000001</v>
       </c>
       <c r="AW7" s="30">
         <f t="shared" si="1"/>
-        <v>1495267.84</v>
+        <v>1548473.9200000002</v>
       </c>
     </row>
     <row r="8" spans="1:49" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -19507,10 +19956,10 @@
         <v>5166.37</v>
       </c>
       <c r="AN8" s="7">
-        <v>0</v>
+        <v>91.44</v>
       </c>
       <c r="AO8" s="7">
-        <v>0</v>
+        <v>91.44</v>
       </c>
       <c r="AP8" s="7">
         <v>0</v>
@@ -19532,11 +19981,11 @@
       </c>
       <c r="AV8" s="7">
         <f t="shared" si="0"/>
-        <v>15542.3</v>
+        <v>15633.74</v>
       </c>
       <c r="AW8" s="28">
         <f t="shared" si="1"/>
-        <v>15542.3</v>
+        <v>15633.74</v>
       </c>
     </row>
     <row r="9" spans="1:49" x14ac:dyDescent="0.25">
@@ -19658,10 +20107,10 @@
         <v>5166.37</v>
       </c>
       <c r="AN9" s="8">
-        <v>0</v>
+        <v>91.44</v>
       </c>
       <c r="AO9" s="9">
-        <v>0</v>
+        <v>91.44</v>
       </c>
       <c r="AP9" s="8">
         <v>0</v>
@@ -19683,11 +20132,11 @@
       </c>
       <c r="AV9" s="8">
         <f t="shared" si="0"/>
-        <v>15542.3</v>
+        <v>15633.74</v>
       </c>
       <c r="AW9" s="30">
         <f t="shared" si="1"/>
-        <v>15542.3</v>
+        <v>15633.74</v>
       </c>
     </row>
     <row r="10" spans="1:49" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -19809,10 +20258,10 @@
         <v>497.86</v>
       </c>
       <c r="AN10" s="7">
-        <v>0</v>
+        <v>464.43</v>
       </c>
       <c r="AO10" s="7">
-        <v>0</v>
+        <v>434.96</v>
       </c>
       <c r="AP10" s="7">
         <v>0</v>
@@ -19834,11 +20283,11 @@
       </c>
       <c r="AV10" s="7">
         <f t="shared" si="0"/>
-        <v>52058.81</v>
+        <v>52523.24</v>
       </c>
       <c r="AW10" s="28">
         <f t="shared" si="1"/>
-        <v>52088.28</v>
+        <v>52523.24</v>
       </c>
     </row>
     <row r="11" spans="1:49" x14ac:dyDescent="0.25">
@@ -19960,10 +20409,10 @@
         <v>497.86</v>
       </c>
       <c r="AN11" s="8">
-        <v>0</v>
+        <v>464.43</v>
       </c>
       <c r="AO11" s="9">
-        <v>0</v>
+        <v>434.96</v>
       </c>
       <c r="AP11" s="8">
         <v>0</v>
@@ -19985,11 +20434,11 @@
       </c>
       <c r="AV11" s="8">
         <f t="shared" si="0"/>
-        <v>4408.47</v>
+        <v>4872.9000000000005</v>
       </c>
       <c r="AW11" s="30">
         <f t="shared" si="1"/>
-        <v>4437.9400000000005</v>
+        <v>4872.9000000000005</v>
       </c>
     </row>
     <row r="12" spans="1:49" x14ac:dyDescent="0.25">
@@ -20515,8 +20964,12 @@
       <c r="AM15" s="7">
         <v>7196.25</v>
       </c>
-      <c r="AN15" s="7"/>
-      <c r="AO15" s="7"/>
+      <c r="AN15" s="7">
+        <v>472.15</v>
+      </c>
+      <c r="AO15" s="7">
+        <v>472.15</v>
+      </c>
       <c r="AP15" s="7"/>
       <c r="AQ15" s="7"/>
       <c r="AR15" s="7"/>
@@ -20525,11 +20978,11 @@
       <c r="AU15" s="7"/>
       <c r="AV15" s="7">
         <f t="shared" si="0"/>
-        <v>18496.25</v>
+        <v>18968.400000000001</v>
       </c>
       <c r="AW15" s="28">
         <f t="shared" si="1"/>
-        <v>18496.25</v>
+        <v>18968.400000000001</v>
       </c>
     </row>
     <row r="16" spans="1:49" x14ac:dyDescent="0.25">
@@ -20753,8 +21206,12 @@
       <c r="AM17" s="9">
         <v>7196.25</v>
       </c>
-      <c r="AN17" s="8"/>
-      <c r="AO17" s="9"/>
+      <c r="AN17" s="8">
+        <v>472.15</v>
+      </c>
+      <c r="AO17" s="9">
+        <v>472.15</v>
+      </c>
       <c r="AP17" s="8"/>
       <c r="AQ17" s="9"/>
       <c r="AR17" s="8"/>
@@ -20763,11 +21220,11 @@
       <c r="AU17" s="9"/>
       <c r="AV17" s="8">
         <f t="shared" si="0"/>
-        <v>19050.059999999998</v>
+        <v>19522.21</v>
       </c>
       <c r="AW17" s="30">
         <f t="shared" si="1"/>
-        <v>19050.059999999998</v>
+        <v>19522.21</v>
       </c>
     </row>
     <row r="18" spans="1:49" ht="15.75" x14ac:dyDescent="0.25">
@@ -20889,10 +21346,10 @@
         <v>-88007.82</v>
       </c>
       <c r="AN18" s="10">
-        <v>-27392.75</v>
+        <v>-113064.01</v>
       </c>
       <c r="AO18" s="10">
-        <v>0</v>
+        <v>-113064.01</v>
       </c>
       <c r="AP18" s="10">
         <v>-27159.79</v>
@@ -20914,11 +21371,11 @@
       </c>
       <c r="AV18" s="10">
         <f t="shared" si="0"/>
-        <v>-1362279.52</v>
+        <v>-1447950.78</v>
       </c>
       <c r="AW18" s="33">
         <f t="shared" si="1"/>
-        <v>-1254805.93</v>
+        <v>-1367869.94</v>
       </c>
     </row>
     <row r="19" spans="1:49" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -21040,10 +21497,10 @@
         <v>-20326.27</v>
       </c>
       <c r="AN19" s="7">
-        <v>-5000</v>
+        <v>-9045.48</v>
       </c>
       <c r="AO19" s="7">
-        <v>0</v>
+        <v>-9045.48</v>
       </c>
       <c r="AP19" s="7">
         <v>-5000</v>
@@ -21065,11 +21522,11 @@
       </c>
       <c r="AV19" s="7">
         <f t="shared" si="0"/>
-        <v>-178969.78</v>
+        <v>-183015.26</v>
       </c>
       <c r="AW19" s="28">
         <f t="shared" si="1"/>
-        <v>-158987.57</v>
+        <v>-168033.05000000002</v>
       </c>
     </row>
     <row r="20" spans="1:49" x14ac:dyDescent="0.25">
@@ -21191,10 +21648,10 @@
         <v>-20326.27</v>
       </c>
       <c r="AN20" s="8">
-        <v>-5000</v>
+        <v>-9045.48</v>
       </c>
       <c r="AO20" s="9">
-        <v>0</v>
+        <v>-9045.48</v>
       </c>
       <c r="AP20" s="8">
         <v>-5000</v>
@@ -21216,11 +21673,11 @@
       </c>
       <c r="AV20" s="8">
         <f t="shared" si="0"/>
-        <v>-178969.78</v>
+        <v>-183015.26</v>
       </c>
       <c r="AW20" s="30">
         <f t="shared" si="1"/>
-        <v>-158987.57</v>
+        <v>-168033.05000000002</v>
       </c>
     </row>
     <row r="21" spans="1:49" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -21342,10 +21799,10 @@
         <v>-124.15</v>
       </c>
       <c r="AN21" s="7">
-        <v>-124.15</v>
+        <v>-2224.15</v>
       </c>
       <c r="AO21" s="7">
-        <v>0</v>
+        <v>-2224.15</v>
       </c>
       <c r="AP21" s="7">
         <v>-124.15</v>
@@ -21367,11 +21824,11 @@
       </c>
       <c r="AV21" s="7">
         <f t="shared" si="0"/>
-        <v>-54643.61</v>
+        <v>-56743.61</v>
       </c>
       <c r="AW21" s="28">
         <f t="shared" si="1"/>
-        <v>-54271.159999999996</v>
+        <v>-56495.31</v>
       </c>
     </row>
     <row r="22" spans="1:49" x14ac:dyDescent="0.25">
@@ -21493,10 +21950,10 @@
         <v>-124.15</v>
       </c>
       <c r="AN22" s="8">
-        <v>-124.15</v>
+        <v>-2224.15</v>
       </c>
       <c r="AO22" s="9">
-        <v>0</v>
+        <v>-2224.15</v>
       </c>
       <c r="AP22" s="8">
         <v>-124.15</v>
@@ -21518,11 +21975,11 @@
       </c>
       <c r="AV22" s="8">
         <f t="shared" si="0"/>
-        <v>-30091.820000000018</v>
+        <v>-32191.820000000018</v>
       </c>
       <c r="AW22" s="30">
         <f t="shared" si="1"/>
-        <v>-29719.370000000014</v>
+        <v>-31943.520000000015</v>
       </c>
     </row>
     <row r="23" spans="1:49" x14ac:dyDescent="0.25">
@@ -21795,10 +22252,10 @@
         <v>-42445.55</v>
       </c>
       <c r="AN24" s="7">
-        <v>-6117.73</v>
+        <v>-65385.66</v>
       </c>
       <c r="AO24" s="7">
-        <v>0</v>
+        <v>-65385.66</v>
       </c>
       <c r="AP24" s="7">
         <v>-6117.73</v>
@@ -21820,11 +22277,11 @@
       </c>
       <c r="AV24" s="7">
         <f t="shared" si="0"/>
-        <v>-551858.11</v>
+        <v>-611126.04</v>
       </c>
       <c r="AW24" s="28">
         <f t="shared" si="1"/>
-        <v>-528622.65</v>
+        <v>-594008.31000000006</v>
       </c>
     </row>
     <row r="25" spans="1:49" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -21946,10 +22403,10 @@
         <v>-41242.44</v>
       </c>
       <c r="AN25" s="11">
-        <v>-2500</v>
+        <v>-64747.96</v>
       </c>
       <c r="AO25" s="12">
-        <v>0</v>
+        <v>-64747.96</v>
       </c>
       <c r="AP25" s="11">
         <v>-2500</v>
@@ -21971,11 +22428,11 @@
       </c>
       <c r="AV25" s="11">
         <f t="shared" si="0"/>
-        <v>-484054.18</v>
+        <v>-546302.14</v>
       </c>
       <c r="AW25" s="35">
         <f t="shared" si="1"/>
-        <v>-474054.18</v>
+        <v>-538802.14</v>
       </c>
     </row>
     <row r="26" spans="1:49" x14ac:dyDescent="0.25">
@@ -22097,7 +22554,7 @@
         <v>-1930</v>
       </c>
       <c r="AN26" s="8">
-        <v>-2500</v>
+        <v>0</v>
       </c>
       <c r="AO26" s="9">
         <v>0</v>
@@ -22122,7 +22579,7 @@
       </c>
       <c r="AV26" s="8">
         <f t="shared" si="0"/>
-        <v>-51930</v>
+        <v>-49430</v>
       </c>
       <c r="AW26" s="30">
         <f t="shared" si="1"/>
@@ -22248,10 +22705,10 @@
         <v>-39312.44</v>
       </c>
       <c r="AN27" s="8">
-        <v>0</v>
+        <v>-64747.96</v>
       </c>
       <c r="AO27" s="9">
-        <v>0</v>
+        <v>-64747.96</v>
       </c>
       <c r="AP27" s="8">
         <v>0</v>
@@ -22273,11 +22730,11 @@
       </c>
       <c r="AV27" s="8">
         <f t="shared" si="0"/>
-        <v>-430089.85000000003</v>
+        <v>-494837.81000000006</v>
       </c>
       <c r="AW27" s="30">
         <f t="shared" si="1"/>
-        <v>-430089.85000000003</v>
+        <v>-494837.81000000006</v>
       </c>
     </row>
     <row r="28" spans="1:49" x14ac:dyDescent="0.25">
@@ -22502,10 +22959,10 @@
         <v>-1203.1099999999999</v>
       </c>
       <c r="AN29" s="11">
-        <v>-3617.73</v>
+        <v>-637.70000000000005</v>
       </c>
       <c r="AO29" s="12">
-        <v>0</v>
+        <v>-637.70000000000005</v>
       </c>
       <c r="AP29" s="11">
         <v>-3617.73</v>
@@ -22527,11 +22984,11 @@
       </c>
       <c r="AV29" s="11">
         <f t="shared" si="0"/>
-        <v>-67803.930000000008</v>
+        <v>-64823.9</v>
       </c>
       <c r="AW29" s="35">
         <f t="shared" si="1"/>
-        <v>-54568.47</v>
+        <v>-55206.17</v>
       </c>
     </row>
     <row r="30" spans="1:49" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -23105,10 +23562,10 @@
         <v>-1201.1199999999999</v>
       </c>
       <c r="AN34" s="8">
-        <v>-617.73</v>
+        <v>-637.70000000000005</v>
       </c>
       <c r="AO34" s="9">
-        <v>0</v>
+        <v>-637.70000000000005</v>
       </c>
       <c r="AP34" s="8">
         <v>-617.73</v>
@@ -23130,11 +23587,11 @@
       </c>
       <c r="AV34" s="8">
         <f t="shared" si="0"/>
-        <v>-46150.320000000007</v>
+        <v>-46170.29</v>
       </c>
       <c r="AW34" s="30">
         <f t="shared" si="1"/>
-        <v>-44914.86</v>
+        <v>-45552.56</v>
       </c>
     </row>
     <row r="35" spans="1:49" x14ac:dyDescent="0.25">
@@ -23383,10 +23840,10 @@
         <v>-13204.01</v>
       </c>
       <c r="AN36" s="7">
-        <v>-11150.87</v>
+        <v>-7146.57</v>
       </c>
       <c r="AO36" s="7">
-        <v>0</v>
+        <v>-7146.57</v>
       </c>
       <c r="AP36" s="7">
         <v>-10917.91</v>
@@ -23408,11 +23865,11 @@
       </c>
       <c r="AV36" s="7">
         <f t="shared" si="0"/>
-        <v>-323148.20999999996</v>
+        <v>-319143.90999999997</v>
       </c>
       <c r="AW36" s="28">
         <f t="shared" si="1"/>
-        <v>-279264.74000000005</v>
+        <v>-286411.31000000006</v>
       </c>
     </row>
     <row r="37" spans="1:49" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -23534,10 +23991,10 @@
         <v>-4411.72</v>
       </c>
       <c r="AN37" s="11">
-        <v>-4281.75</v>
+        <v>-4316.51</v>
       </c>
       <c r="AO37" s="12">
-        <v>0</v>
+        <v>-4316.51</v>
       </c>
       <c r="AP37" s="11">
         <v>-4281.75</v>
@@ -23559,11 +24016,11 @@
       </c>
       <c r="AV37" s="11">
         <f t="shared" si="0"/>
-        <v>-92777.78</v>
+        <v>-92812.54</v>
       </c>
       <c r="AW37" s="35">
         <f t="shared" si="1"/>
-        <v>-75638.439999999988</v>
+        <v>-79954.949999999983</v>
       </c>
     </row>
     <row r="38" spans="1:49" x14ac:dyDescent="0.25">
@@ -23688,7 +24145,7 @@
         <v>-1100</v>
       </c>
       <c r="AO38" s="9">
-        <v>0</v>
+        <v>-1100</v>
       </c>
       <c r="AP38" s="8">
         <v>-1100</v>
@@ -23714,7 +24171,7 @@
       </c>
       <c r="AW38" s="30">
         <f t="shared" si="1"/>
-        <v>-14600</v>
+        <v>-15700</v>
       </c>
     </row>
     <row r="39" spans="1:49" x14ac:dyDescent="0.25">
@@ -23839,7 +24296,7 @@
         <v>-1350</v>
       </c>
       <c r="AO39" s="9">
-        <v>0</v>
+        <v>-1350</v>
       </c>
       <c r="AP39" s="8">
         <v>-1350</v>
@@ -23865,7 +24322,7 @@
       </c>
       <c r="AW39" s="30">
         <f t="shared" si="1"/>
-        <v>-25537.5</v>
+        <v>-26887.5</v>
       </c>
     </row>
     <row r="40" spans="1:49" x14ac:dyDescent="0.25">
@@ -23987,10 +24444,10 @@
         <v>-420.1</v>
       </c>
       <c r="AN40" s="8">
-        <v>-300</v>
+        <v>-327.51</v>
       </c>
       <c r="AO40" s="9">
-        <v>0</v>
+        <v>-327.51</v>
       </c>
       <c r="AP40" s="8">
         <v>-300</v>
@@ -24012,11 +24469,11 @@
       </c>
       <c r="AV40" s="8">
         <f t="shared" si="0"/>
-        <v>-8103.96</v>
+        <v>-8131.47</v>
       </c>
       <c r="AW40" s="30">
         <f t="shared" si="1"/>
-        <v>-6903.96</v>
+        <v>-7231.47</v>
       </c>
     </row>
     <row r="41" spans="1:49" x14ac:dyDescent="0.25">
@@ -24141,7 +24598,7 @@
         <v>-1200</v>
       </c>
       <c r="AO41" s="9">
-        <v>0</v>
+        <v>-1200</v>
       </c>
       <c r="AP41" s="8">
         <v>-1200</v>
@@ -24167,7 +24624,7 @@
       </c>
       <c r="AW41" s="30">
         <f t="shared" si="1"/>
-        <v>-22684.75</v>
+        <v>-23884.75</v>
       </c>
     </row>
     <row r="42" spans="1:49" x14ac:dyDescent="0.25">
@@ -24289,10 +24746,10 @@
         <v>-210</v>
       </c>
       <c r="AN42" s="8">
-        <v>-200</v>
+        <v>-210</v>
       </c>
       <c r="AO42" s="9">
-        <v>0</v>
+        <v>-210</v>
       </c>
       <c r="AP42" s="8">
         <v>-200</v>
@@ -24314,11 +24771,11 @@
       </c>
       <c r="AV42" s="8">
         <f t="shared" si="0"/>
-        <v>-4367.1399999999994</v>
+        <v>-4377.1399999999994</v>
       </c>
       <c r="AW42" s="30">
         <f t="shared" si="1"/>
-        <v>-3564.6</v>
+        <v>-3774.6</v>
       </c>
     </row>
     <row r="43" spans="1:49" x14ac:dyDescent="0.25">
@@ -24440,10 +24897,10 @@
         <v>-131.62</v>
       </c>
       <c r="AN43" s="8">
-        <v>-131.75</v>
+        <v>-129</v>
       </c>
       <c r="AO43" s="9">
-        <v>0</v>
+        <v>-129</v>
       </c>
       <c r="AP43" s="8">
         <v>-131.75</v>
@@ -24465,11 +24922,11 @@
       </c>
       <c r="AV43" s="8">
         <f t="shared" si="0"/>
-        <v>-2869.18</v>
+        <v>-2866.43</v>
       </c>
       <c r="AW43" s="30">
         <f t="shared" si="1"/>
-        <v>-2347.6299999999997</v>
+        <v>-2476.6299999999997</v>
       </c>
     </row>
     <row r="44" spans="1:49" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -24591,10 +25048,10 @@
         <v>-6785.63</v>
       </c>
       <c r="AN44" s="11">
-        <v>-6636.16</v>
+        <v>-1654.47</v>
       </c>
       <c r="AO44" s="12">
-        <v>0</v>
+        <v>-1654.47</v>
       </c>
       <c r="AP44" s="11">
         <v>-6636.16</v>
@@ -24616,11 +25073,11 @@
       </c>
       <c r="AV44" s="11">
         <f t="shared" si="0"/>
-        <v>-180264.62000000002</v>
+        <v>-175282.93000000002</v>
       </c>
       <c r="AW44" s="35">
         <f t="shared" si="1"/>
-        <v>-153753.45000000001</v>
+        <v>-155407.92000000001</v>
       </c>
     </row>
     <row r="45" spans="1:49" x14ac:dyDescent="0.25">
@@ -24745,7 +25202,7 @@
         <v>-33.47</v>
       </c>
       <c r="AO45" s="9">
-        <v>0</v>
+        <v>-33.47</v>
       </c>
       <c r="AP45" s="8">
         <v>-33.47</v>
@@ -24771,7 +25228,7 @@
       </c>
       <c r="AW45" s="30">
         <f t="shared" si="1"/>
-        <v>-5661.28</v>
+        <v>-5694.75</v>
       </c>
     </row>
     <row r="46" spans="1:49" x14ac:dyDescent="0.25">
@@ -24893,7 +25350,7 @@
         <v>-4501.45</v>
       </c>
       <c r="AN46" s="8">
-        <v>-5000</v>
+        <v>0</v>
       </c>
       <c r="AO46" s="9">
         <v>0</v>
@@ -24918,7 +25375,7 @@
       </c>
       <c r="AV46" s="8">
         <f t="shared" si="0"/>
-        <v>-141495.62</v>
+        <v>-136495.62</v>
       </c>
       <c r="AW46" s="30">
         <f t="shared" si="1"/>
@@ -25044,10 +25501,10 @@
         <v>-178.31</v>
       </c>
       <c r="AN47" s="8">
-        <v>-160</v>
+        <v>-178.31</v>
       </c>
       <c r="AO47" s="9">
-        <v>0</v>
+        <v>-178.31</v>
       </c>
       <c r="AP47" s="8">
         <v>-160</v>
@@ -25069,11 +25526,11 @@
       </c>
       <c r="AV47" s="8">
         <f t="shared" si="0"/>
-        <v>-3557.97</v>
+        <v>-3576.2799999999997</v>
       </c>
       <c r="AW47" s="30">
         <f t="shared" si="1"/>
-        <v>-2917.97</v>
+        <v>-3096.2799999999997</v>
       </c>
     </row>
     <row r="48" spans="1:49" x14ac:dyDescent="0.25">
@@ -25198,7 +25655,7 @@
         <v>-1442.69</v>
       </c>
       <c r="AO48" s="9">
-        <v>0</v>
+        <v>-1442.69</v>
       </c>
       <c r="AP48" s="8">
         <v>-1442.69</v>
@@ -25224,7 +25681,7 @@
       </c>
       <c r="AW48" s="30">
         <f t="shared" si="1"/>
-        <v>-21983</v>
+        <v>-23425.69</v>
       </c>
     </row>
     <row r="49" spans="1:49" x14ac:dyDescent="0.25">
@@ -25453,10 +25910,10 @@
         <v>-2006.66</v>
       </c>
       <c r="AN50" s="11">
-        <v>-232.96</v>
+        <v>-1175.5899999999999</v>
       </c>
       <c r="AO50" s="12">
-        <v>0</v>
+        <v>-1175.5899999999999</v>
       </c>
       <c r="AP50" s="11">
         <v>0</v>
@@ -25478,11 +25935,11 @@
       </c>
       <c r="AV50" s="11">
         <f t="shared" si="0"/>
-        <v>-50105.81</v>
+        <v>-51048.439999999995</v>
       </c>
       <c r="AW50" s="35">
         <f t="shared" si="1"/>
-        <v>-49872.85</v>
+        <v>-51048.439999999995</v>
       </c>
     </row>
     <row r="51" spans="1:49" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -26354,10 +26811,10 @@
         <v>-764.88</v>
       </c>
       <c r="AN57" s="8">
-        <v>-227.89</v>
+        <v>-227.88</v>
       </c>
       <c r="AO57" s="9">
-        <v>0</v>
+        <v>-227.88</v>
       </c>
       <c r="AP57" s="8">
         <v>0</v>
@@ -26379,11 +26836,11 @@
       </c>
       <c r="AV57" s="8">
         <f t="shared" si="0"/>
-        <v>-20612.330000000002</v>
+        <v>-20612.320000000003</v>
       </c>
       <c r="AW57" s="30">
         <f t="shared" si="1"/>
-        <v>-20384.440000000002</v>
+        <v>-20612.320000000003</v>
       </c>
     </row>
     <row r="58" spans="1:49" x14ac:dyDescent="0.25">
@@ -26505,10 +26962,10 @@
         <v>-1211.8</v>
       </c>
       <c r="AN58" s="8">
-        <v>-5.07</v>
+        <v>-947.71</v>
       </c>
       <c r="AO58" s="9">
-        <v>0</v>
+        <v>-947.71</v>
       </c>
       <c r="AP58" s="8">
         <v>0</v>
@@ -26530,11 +26987,11 @@
       </c>
       <c r="AV58" s="8">
         <f t="shared" si="0"/>
-        <v>-10814.09</v>
+        <v>-11756.73</v>
       </c>
       <c r="AW58" s="30">
         <f t="shared" si="1"/>
-        <v>-10809.02</v>
+        <v>-11756.73</v>
       </c>
     </row>
     <row r="59" spans="1:49" x14ac:dyDescent="0.25">
@@ -27692,10 +28149,10 @@
         <v>-64.73</v>
       </c>
       <c r="AN67" s="7">
-        <v>0</v>
+        <v>-42.15</v>
       </c>
       <c r="AO67" s="7">
-        <v>0</v>
+        <v>-42.15</v>
       </c>
       <c r="AP67" s="7">
         <v>0</v>
@@ -27717,11 +28174,11 @@
       </c>
       <c r="AV67" s="7">
         <f t="shared" si="0"/>
-        <v>-2984.82</v>
+        <v>-3026.9700000000003</v>
       </c>
       <c r="AW67" s="28">
         <f t="shared" si="1"/>
-        <v>-2984.82</v>
+        <v>-3026.9700000000003</v>
       </c>
     </row>
     <row r="68" spans="1:49" x14ac:dyDescent="0.25">
@@ -27843,10 +28300,10 @@
         <v>-64.73</v>
       </c>
       <c r="AN68" s="8">
-        <v>0</v>
+        <v>-42.15</v>
       </c>
       <c r="AO68" s="9">
-        <v>0</v>
+        <v>-42.15</v>
       </c>
       <c r="AP68" s="8">
         <v>0</v>
@@ -27868,11 +28325,11 @@
       </c>
       <c r="AV68" s="8">
         <f t="shared" si="0"/>
-        <v>-495.50000000000011</v>
+        <v>-537.65000000000009</v>
       </c>
       <c r="AW68" s="30">
         <f t="shared" si="1"/>
-        <v>-495.50000000000011</v>
+        <v>-537.65000000000009</v>
       </c>
     </row>
     <row r="69" spans="1:49" x14ac:dyDescent="0.25">
@@ -28371,10 +28828,10 @@
         <v>-10989.65</v>
       </c>
       <c r="AN72" s="7">
-        <v>-5000</v>
+        <v>-29220</v>
       </c>
       <c r="AO72" s="7">
-        <v>0</v>
+        <v>-29220</v>
       </c>
       <c r="AP72" s="7">
         <v>-5000</v>
@@ -28396,11 +28853,11 @@
       </c>
       <c r="AV72" s="7">
         <f t="shared" si="2"/>
-        <v>-99855.59</v>
+        <v>-124075.59</v>
       </c>
       <c r="AW72" s="28">
         <f t="shared" si="3"/>
-        <v>-79855.59</v>
+        <v>-109075.59</v>
       </c>
     </row>
     <row r="73" spans="1:49" s="14" customFormat="1" x14ac:dyDescent="0.25">
@@ -28474,10 +28931,10 @@
         <v>-5989.65</v>
       </c>
       <c r="AN73" s="8">
-        <v>0</v>
+        <v>-24220</v>
       </c>
       <c r="AO73" s="9">
-        <v>0</v>
+        <v>-24220</v>
       </c>
       <c r="AP73" s="8">
         <v>0</v>
@@ -28500,7 +28957,7 @@
       <c r="AV73" s="8"/>
       <c r="AW73" s="30">
         <f t="shared" si="3"/>
-        <v>-5989.65</v>
+        <v>-30209.65</v>
       </c>
     </row>
     <row r="74" spans="1:49" x14ac:dyDescent="0.25">
@@ -28708,7 +29165,7 @@
         <v>-5000</v>
       </c>
       <c r="AO75" s="9">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="AP75" s="8">
         <v>-5000</v>
@@ -29148,7 +29605,7 @@
         <v>0</v>
       </c>
       <c r="AV78" s="8">
-        <f t="shared" si="2"/>
+        <f>SUM(B78+D78+F78+H78+J78+L78+N78+P78+R78+T78+V78+X78+Z78+AB78+AD78+AF78+AH78+AJ78+AL78+AN78+AP78+AR78+AT78)</f>
         <v>-148592.10000000003</v>
       </c>
       <c r="AW78" s="30">
@@ -29275,10 +29732,10 @@
         <v>-7887.53</v>
       </c>
       <c r="AN79" s="41">
-        <v>3484.99</v>
+        <v>-54674.57</v>
       </c>
       <c r="AO79" s="5">
-        <v>0</v>
+        <v>-58859.38</v>
       </c>
       <c r="AP79" s="41">
         <v>-16303.44</v>
@@ -29420,10 +29877,10 @@
         <v>422285.84</v>
       </c>
       <c r="AN80" s="42">
-        <v>650579.51</v>
+        <v>548132.64</v>
       </c>
       <c r="AO80" s="39">
-        <v>444032.13</v>
+        <v>364059.74</v>
       </c>
       <c r="AP80" s="42">
         <v>634276.06999999995</v>
@@ -29448,18 +29905,6 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="R1:S1"/>
-    <mergeCell ref="AH1:AI1"/>
-    <mergeCell ref="AD1:AE1"/>
-    <mergeCell ref="AF1:AG1"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="J1:K1"/>
     <mergeCell ref="AV1:AW1"/>
     <mergeCell ref="T1:U1"/>
     <mergeCell ref="V1:W1"/>
@@ -29472,6 +29917,18 @@
     <mergeCell ref="AP1:AQ1"/>
     <mergeCell ref="AR1:AS1"/>
     <mergeCell ref="AT1:AU1"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="AH1:AI1"/>
+    <mergeCell ref="AD1:AE1"/>
+    <mergeCell ref="AF1:AG1"/>
   </mergeCells>
   <conditionalFormatting sqref="A4:AW4">
     <cfRule type="cellIs" dxfId="5" priority="5" operator="greaterThan">
@@ -29553,7 +30010,7 @@
         <v>121</v>
       </c>
       <c r="B2" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="C2" s="2">
         <v>998.5</v>
@@ -29564,7 +30021,7 @@
         <v>121</v>
       </c>
       <c r="B3" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="C3" s="2">
         <v>998.5</v>
@@ -29575,7 +30032,7 @@
         <v>122</v>
       </c>
       <c r="B4" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="C4" s="2">
         <v>648.5</v>
@@ -29586,7 +30043,7 @@
         <v>123</v>
       </c>
       <c r="B5" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="C5" s="2">
         <v>843.67</v>
@@ -29597,7 +30054,7 @@
         <v>123</v>
       </c>
       <c r="B6" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="C6" s="2">
         <v>843.67</v>
@@ -29605,10 +30062,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>160</v>
+        <v>143</v>
       </c>
       <c r="B7" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="C7" s="2">
         <v>875.75</v>
@@ -29619,7 +30076,7 @@
         <v>124</v>
       </c>
       <c r="B8" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="C8" s="2">
         <v>921.61</v>
@@ -29630,7 +30087,7 @@
         <v>125</v>
       </c>
       <c r="B9" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="C9" s="2">
         <v>465.09</v>
@@ -29641,7 +30098,7 @@
         <v>126</v>
       </c>
       <c r="B10" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="C10" s="2">
         <v>1329</v>
@@ -29652,7 +30109,7 @@
         <v>127</v>
       </c>
       <c r="B11" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="C11" s="2">
         <v>198.5</v>
@@ -29663,7 +30120,7 @@
         <v>124</v>
       </c>
       <c r="B12" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="C12" s="2">
         <v>921.61</v>
@@ -29671,10 +30128,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>160</v>
+        <v>143</v>
       </c>
       <c r="B13" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C13" s="2">
         <v>875.75</v>
@@ -29696,7 +30153,7 @@
         <v>130</v>
       </c>
       <c r="B15" t="s">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="C15" s="2">
         <v>999.25</v>
@@ -29704,112 +30161,112 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B16" t="s">
-        <v>152</v>
+        <v>138</v>
       </c>
       <c r="C16" s="2">
-        <v>600</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="B17" t="s">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="C17" s="2">
-        <v>1329</v>
+        <v>1993.57</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="B18" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="C18" s="2">
-        <v>759.42</v>
+        <v>921.61</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B19" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="C19" s="2">
-        <v>1993.57</v>
+        <v>1266.6600000000001</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B20" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="C20" s="2">
-        <v>749.25</v>
+        <v>1091.9000000000001</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="B21" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="C21" s="2">
-        <v>921.61</v>
+        <v>600</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="B22" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="C22" s="2">
-        <v>1249.25</v>
+        <v>499.25</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B23" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="C23" s="2">
-        <v>850.75</v>
+        <v>1091.9000000000001</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="B24" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="C24" s="2">
-        <v>1266.6600000000001</v>
+        <v>759.42</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="B25" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C25" s="2">
-        <v>1091.9000000000001</v>
+        <v>759.42</v>
       </c>
     </row>
   </sheetData>
